--- a/B&B Inventory_Master_List.xlsx
+++ b/B&B Inventory_Master_List.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\johnw\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://netorgft7663837-my.sharepoint.com/personal/jsebastian_bandbconcrete_com/Documents/B&amp;B Concrete Enterprises, Inc/9 - IT/02 - In House Tools/1 - AI App/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31F3C067-D2E3-4EF3-83E9-1AAF68E48091}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="142" documentId="13_ncr:1_{31F3C067-D2E3-4EF3-83E9-1AAF68E48091}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FCA27391-F2AE-44F8-9F3A-9A2A917EE922}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inventory" sheetId="1" r:id="rId1"/>
-    <sheet name="Vendor" sheetId="2" r:id="rId2"/>
-    <sheet name="Projects" sheetId="3" r:id="rId3"/>
-    <sheet name="Customer" sheetId="4" r:id="rId4"/>
+    <sheet name="Employees" sheetId="5" r:id="rId2"/>
+    <sheet name="Vendor" sheetId="2" r:id="rId3"/>
+    <sheet name="Projects" sheetId="3" r:id="rId4"/>
+    <sheet name="Customer" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,18 +37,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="844" uniqueCount="547">
   <si>
     <t>Product Name</t>
   </si>
   <si>
     <t>Category</t>
-  </si>
-  <si>
-    <t>SKU</t>
-  </si>
-  <si>
-    <t>Unit of Measure</t>
   </si>
   <si>
     <t>CDX Plywood 1/2 in</t>
@@ -1510,13 +1505,190 @@
   </si>
   <si>
     <t>Brennan Const</t>
+  </si>
+  <si>
+    <t>Item No</t>
+  </si>
+  <si>
+    <t>UOM</t>
+  </si>
+  <si>
+    <t>Employee</t>
+  </si>
+  <si>
+    <t>John Wesley Sebastian</t>
+  </si>
+  <si>
+    <t>Timothy Hoey</t>
+  </si>
+  <si>
+    <t>Jerin Lesley Sebastian</t>
+  </si>
+  <si>
+    <t>Gilma Kelly</t>
+  </si>
+  <si>
+    <t>Winder L Alvarez</t>
+  </si>
+  <si>
+    <t>Julio C Alvarracin</t>
+  </si>
+  <si>
+    <t>Segundo E Castillo</t>
+  </si>
+  <si>
+    <t>Jaime L Criollo</t>
+  </si>
+  <si>
+    <t>Juan C Duchi</t>
+  </si>
+  <si>
+    <t>Miguel Espinoza</t>
+  </si>
+  <si>
+    <t>Rui Fidalgo</t>
+  </si>
+  <si>
+    <t>Patricio F Guallpa</t>
+  </si>
+  <si>
+    <t>Segundo I Naula</t>
+  </si>
+  <si>
+    <t>Justo G Paredes</t>
+  </si>
+  <si>
+    <t>Darwin J Rivas</t>
+  </si>
+  <si>
+    <t>Colin Smallman</t>
+  </si>
+  <si>
+    <t>Luis A Urgiles</t>
+  </si>
+  <si>
+    <t>Fernando M Urgiles</t>
+  </si>
+  <si>
+    <t>Freddy A Estrada</t>
+  </si>
+  <si>
+    <t>Geoffrey Duval</t>
+  </si>
+  <si>
+    <t>John S Cappelli</t>
+  </si>
+  <si>
+    <t>David Monastersky</t>
+  </si>
+  <si>
+    <t>Keith R Irish</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roger Aleman </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flaviano Alvez Demoura </t>
+  </si>
+  <si>
+    <t>Wilfrido Andy</t>
+  </si>
+  <si>
+    <t>Matheus Assuncao DeSa</t>
+  </si>
+  <si>
+    <t>Robert D Baan</t>
+  </si>
+  <si>
+    <t>Joshua L DeGroodt</t>
+  </si>
+  <si>
+    <t>Wanderson Gomes Pereira</t>
+  </si>
+  <si>
+    <t>Faud J Haddad</t>
+  </si>
+  <si>
+    <t>Rolando Lancho</t>
+  </si>
+  <si>
+    <t>James E Luoma</t>
+  </si>
+  <si>
+    <t>Feliz Mejia</t>
+  </si>
+  <si>
+    <t>Brian Vaughan</t>
+  </si>
+  <si>
+    <t>Ronald Zapata</t>
+  </si>
+  <si>
+    <t>Segundo E Zapata</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Position</t>
+  </si>
+  <si>
+    <t>Admin</t>
+  </si>
+  <si>
+    <t>Vincent Jennosa</t>
+  </si>
+  <si>
+    <t>Mathieu Blandin</t>
+  </si>
+  <si>
+    <t>Super Admin</t>
+  </si>
+  <si>
+    <t>Log Inventory</t>
+  </si>
+  <si>
+    <t>Notes:</t>
+  </si>
+  <si>
+    <t>Super Admin should be able to add new people and assign them access</t>
+  </si>
+  <si>
+    <t>Admin should be able to add new items, log inventory in, correct any discrepancy</t>
+  </si>
+  <si>
+    <t>Nyack Lumber, Inc</t>
+  </si>
+  <si>
+    <t>118 Route 59</t>
+  </si>
+  <si>
+    <t>Central Nyack</t>
+  </si>
+  <si>
+    <t>nyacklumberdesk@gmail.com</t>
+  </si>
+  <si>
+    <t>Mike</t>
+  </si>
+  <si>
+    <t>Vendor #</t>
+  </si>
+  <si>
+    <t>Vendor Name</t>
+  </si>
+  <si>
+    <t>Internal Order</t>
+  </si>
+  <si>
+    <t>jerinsebastian@bandbconcrete.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1532,16 +1704,48 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1564,43 +1768,50 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{21108F78-105E-4C7B-955C-5A5203FC95A2}"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1900,779 +2111,1533 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="9" t="s">
+        <v>488</v>
+      </c>
+      <c r="B1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="10" t="s">
+        <v>489</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>543</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="C2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E2">
+        <v>1033</v>
+      </c>
+      <c r="F2" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="C3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3" t="s">
+        <v>101</v>
+      </c>
+      <c r="E3" s="2">
+        <v>1033</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E4" s="2">
+        <v>1033</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" t="s">
+        <v>103</v>
+      </c>
+      <c r="E5" s="2">
+        <v>1033</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D6" t="s">
+        <v>103</v>
+      </c>
+      <c r="E6" s="2">
+        <v>1033</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D7" t="s">
+        <v>104</v>
+      </c>
+      <c r="E7" s="2">
+        <v>1011</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" t="s">
+        <v>104</v>
+      </c>
+      <c r="E8" s="2">
+        <v>1011</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" t="s">
+        <v>101</v>
+      </c>
+      <c r="E9" s="2">
+        <v>1011</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>62</v>
+      </c>
+      <c r="B10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" t="s">
+        <v>101</v>
+      </c>
+      <c r="E10" s="2">
+        <v>1011</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>63</v>
+      </c>
+      <c r="B11" t="s">
+        <v>105</v>
+      </c>
+      <c r="C11" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" t="s">
+        <v>103</v>
+      </c>
+      <c r="E11" s="2">
+        <v>1011</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>64</v>
+      </c>
+      <c r="B12" t="s">
+        <v>106</v>
+      </c>
+      <c r="C12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" t="s">
+        <v>103</v>
+      </c>
+      <c r="E12" s="2">
+        <v>1011</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>65</v>
+      </c>
+      <c r="B13" t="s">
+        <v>107</v>
+      </c>
+      <c r="C13" t="s">
+        <v>47</v>
+      </c>
+      <c r="D13" t="s">
+        <v>103</v>
+      </c>
+      <c r="E13" s="2">
+        <v>1011</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>66</v>
+      </c>
+      <c r="B14" t="s">
+        <v>108</v>
+      </c>
+      <c r="C14" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" t="s">
+        <v>103</v>
+      </c>
+      <c r="E14" s="2">
+        <v>1011</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>67</v>
+      </c>
+      <c r="B15" t="s">
+        <v>109</v>
+      </c>
+      <c r="C15" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" t="s">
+        <v>103</v>
+      </c>
+      <c r="E15" s="2">
+        <v>1011</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>68</v>
+      </c>
+      <c r="B16" t="s">
+        <v>110</v>
+      </c>
+      <c r="C16" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" t="s">
+        <v>103</v>
+      </c>
+      <c r="E16" s="2">
+        <v>1011</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>69</v>
+      </c>
+      <c r="B17" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" t="s">
+        <v>47</v>
+      </c>
+      <c r="D17" t="s">
+        <v>112</v>
+      </c>
+      <c r="E17" s="2">
+        <v>1021</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>70</v>
+      </c>
+      <c r="B18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" t="s">
+        <v>47</v>
+      </c>
+      <c r="D18" t="s">
+        <v>111</v>
+      </c>
+      <c r="E18" s="2">
+        <v>1021</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>71</v>
+      </c>
+      <c r="B19" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" t="s">
+        <v>47</v>
+      </c>
+      <c r="D19" t="s">
+        <v>112</v>
+      </c>
+      <c r="E19" s="2">
+        <v>1021</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>72</v>
+      </c>
+      <c r="B20" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" t="s">
         <v>48</v>
       </c>
-      <c r="C2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="D20" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="E20" s="2">
+        <v>1021</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>73</v>
+      </c>
+      <c r="B21" t="s">
+        <v>113</v>
+      </c>
+      <c r="C21" t="s">
         <v>48</v>
       </c>
-      <c r="C3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="D21" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="E21" s="2">
+        <v>1021</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>74</v>
+      </c>
+      <c r="B22" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" t="s">
         <v>48</v>
       </c>
-      <c r="C4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" t="s">
-        <v>48</v>
-      </c>
-      <c r="C5" t="s">
-        <v>59</v>
-      </c>
-      <c r="D5" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C6" t="s">
-        <v>60</v>
-      </c>
-      <c r="D6" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="D22" t="s">
+        <v>103</v>
+      </c>
+      <c r="E22" s="2">
+        <v>1021</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>75</v>
+      </c>
+      <c r="B23" t="s">
+        <v>114</v>
+      </c>
+      <c r="C23" t="s">
         <v>49</v>
       </c>
-      <c r="C7" t="s">
-        <v>61</v>
-      </c>
-      <c r="D7" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="D23" t="s">
+        <v>103</v>
+      </c>
+      <c r="E23" s="2">
+        <v>1021</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>116</v>
+      </c>
+      <c r="B24" t="s">
+        <v>115</v>
+      </c>
+      <c r="C24" t="s">
         <v>49</v>
       </c>
-      <c r="C8" t="s">
-        <v>62</v>
-      </c>
-      <c r="D8" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" t="s">
-        <v>49</v>
-      </c>
-      <c r="C9" t="s">
-        <v>63</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="D24" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" t="s">
-        <v>49</v>
-      </c>
-      <c r="C10" t="s">
-        <v>64</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="E24" s="2">
+        <v>1021</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>76</v>
+      </c>
+      <c r="B25" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" t="s">
+        <v>50</v>
+      </c>
+      <c r="D25" t="s">
+        <v>102</v>
+      </c>
+      <c r="E25" s="2">
+        <v>1021</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>77</v>
+      </c>
+      <c r="B26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26" t="s">
+        <v>50</v>
+      </c>
+      <c r="D26" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>107</v>
-      </c>
-      <c r="B11" t="s">
-        <v>49</v>
-      </c>
-      <c r="C11" t="s">
-        <v>65</v>
-      </c>
-      <c r="D11" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>108</v>
-      </c>
-      <c r="B12" t="s">
-        <v>49</v>
-      </c>
-      <c r="C12" t="s">
-        <v>66</v>
-      </c>
-      <c r="D12" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>109</v>
-      </c>
-      <c r="B13" t="s">
-        <v>49</v>
-      </c>
-      <c r="C13" t="s">
-        <v>67</v>
-      </c>
-      <c r="D13" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>110</v>
-      </c>
-      <c r="B14" t="s">
-        <v>49</v>
-      </c>
-      <c r="C14" t="s">
-        <v>68</v>
-      </c>
-      <c r="D14" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>111</v>
-      </c>
-      <c r="B15" t="s">
-        <v>49</v>
-      </c>
-      <c r="C15" t="s">
-        <v>69</v>
-      </c>
-      <c r="D15" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="E26" s="2">
+        <v>1021</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>78</v>
+      </c>
+      <c r="B27" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" t="s">
+        <v>50</v>
+      </c>
+      <c r="D27" t="s">
+        <v>103</v>
+      </c>
+      <c r="E27" s="2">
+        <v>1021</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>79</v>
+      </c>
+      <c r="B28" t="s">
+        <v>19</v>
+      </c>
+      <c r="C28" t="s">
+        <v>50</v>
+      </c>
+      <c r="D28" t="s">
+        <v>102</v>
+      </c>
+      <c r="E28" s="2">
+        <v>1021</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>80</v>
+      </c>
+      <c r="B29" t="s">
+        <v>20</v>
+      </c>
+      <c r="C29" t="s">
+        <v>50</v>
+      </c>
+      <c r="D29" t="s">
+        <v>102</v>
+      </c>
+      <c r="E29" s="2">
+        <v>1021</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>81</v>
+      </c>
+      <c r="B30" t="s">
+        <v>21</v>
+      </c>
+      <c r="C30" t="s">
+        <v>50</v>
+      </c>
+      <c r="D30" t="s">
         <v>112</v>
       </c>
-      <c r="B16" t="s">
-        <v>49</v>
-      </c>
-      <c r="C16" t="s">
-        <v>70</v>
-      </c>
-      <c r="D16" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>13</v>
-      </c>
-      <c r="B17" t="s">
-        <v>49</v>
-      </c>
-      <c r="C17" t="s">
-        <v>71</v>
-      </c>
-      <c r="D17" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>14</v>
-      </c>
-      <c r="B18" t="s">
-        <v>49</v>
-      </c>
-      <c r="C18" t="s">
-        <v>72</v>
-      </c>
-      <c r="D18" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" t="s">
-        <v>49</v>
-      </c>
-      <c r="C19" t="s">
-        <v>73</v>
-      </c>
-      <c r="D19" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>16</v>
-      </c>
-      <c r="B20" t="s">
+      <c r="E30" s="2">
+        <v>1021</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>82</v>
+      </c>
+      <c r="B31" t="s">
+        <v>22</v>
+      </c>
+      <c r="C31" t="s">
         <v>50</v>
       </c>
-      <c r="C20" t="s">
-        <v>74</v>
-      </c>
-      <c r="D20" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>115</v>
-      </c>
-      <c r="B21" t="s">
+      <c r="D31" t="s">
+        <v>117</v>
+      </c>
+      <c r="E31" s="2">
+        <v>1021</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>83</v>
+      </c>
+      <c r="B32" t="s">
+        <v>23</v>
+      </c>
+      <c r="C32" t="s">
         <v>50</v>
       </c>
-      <c r="C21" t="s">
-        <v>75</v>
-      </c>
-      <c r="D21" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>17</v>
-      </c>
-      <c r="B22" t="s">
-        <v>50</v>
-      </c>
-      <c r="C22" t="s">
-        <v>76</v>
-      </c>
-      <c r="D22" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>116</v>
-      </c>
-      <c r="B23" t="s">
+      <c r="D32" t="s">
+        <v>103</v>
+      </c>
+      <c r="E32" s="2">
+        <v>1021</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>84</v>
+      </c>
+      <c r="B33" t="s">
+        <v>24</v>
+      </c>
+      <c r="C33" t="s">
         <v>51</v>
       </c>
-      <c r="C23" t="s">
-        <v>77</v>
-      </c>
-      <c r="D23" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>117</v>
-      </c>
-      <c r="B24" t="s">
+      <c r="D33" t="s">
+        <v>112</v>
+      </c>
+      <c r="E33" s="2">
+        <v>1021</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>85</v>
+      </c>
+      <c r="B34" t="s">
+        <v>25</v>
+      </c>
+      <c r="C34" t="s">
         <v>51</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D34" t="s">
+        <v>112</v>
+      </c>
+      <c r="E34" s="2">
+        <v>1021</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>86</v>
+      </c>
+      <c r="B35" t="s">
+        <v>26</v>
+      </c>
+      <c r="C35" t="s">
+        <v>51</v>
+      </c>
+      <c r="D35" t="s">
+        <v>112</v>
+      </c>
+      <c r="E35" s="2">
+        <v>1021</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>87</v>
+      </c>
+      <c r="B36" t="s">
+        <v>27</v>
+      </c>
+      <c r="C36" t="s">
+        <v>51</v>
+      </c>
+      <c r="D36" t="s">
+        <v>103</v>
+      </c>
+      <c r="E36" s="2">
+        <v>1021</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>88</v>
+      </c>
+      <c r="B37" t="s">
+        <v>28</v>
+      </c>
+      <c r="C37" t="s">
+        <v>51</v>
+      </c>
+      <c r="D37" t="s">
+        <v>112</v>
+      </c>
+      <c r="E37" s="2">
+        <v>1021</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>89</v>
+      </c>
+      <c r="B38" t="s">
+        <v>29</v>
+      </c>
+      <c r="C38" t="s">
+        <v>51</v>
+      </c>
+      <c r="D38" t="s">
+        <v>103</v>
+      </c>
+      <c r="E38" s="2">
+        <v>1021</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>90</v>
+      </c>
+      <c r="B39" t="s">
+        <v>30</v>
+      </c>
+      <c r="C39" t="s">
+        <v>52</v>
+      </c>
+      <c r="D39" t="s">
+        <v>103</v>
+      </c>
+      <c r="E39" s="2">
+        <v>1000</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>91</v>
+      </c>
+      <c r="B40" t="s">
+        <v>31</v>
+      </c>
+      <c r="C40" t="s">
+        <v>52</v>
+      </c>
+      <c r="D40" t="s">
+        <v>103</v>
+      </c>
+      <c r="E40" s="2">
+        <v>1021</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>92</v>
+      </c>
+      <c r="B41" t="s">
+        <v>32</v>
+      </c>
+      <c r="C41" t="s">
+        <v>53</v>
+      </c>
+      <c r="D41" t="s">
+        <v>103</v>
+      </c>
+      <c r="E41" s="2">
+        <v>1000</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>93</v>
+      </c>
+      <c r="B42" t="s">
+        <v>33</v>
+      </c>
+      <c r="C42" t="s">
+        <v>53</v>
+      </c>
+      <c r="D42" t="s">
+        <v>103</v>
+      </c>
+      <c r="E42" s="2">
+        <v>1000</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>94</v>
+      </c>
+      <c r="B43" t="s">
+        <v>34</v>
+      </c>
+      <c r="C43" t="s">
+        <v>53</v>
+      </c>
+      <c r="D43" t="s">
+        <v>103</v>
+      </c>
+      <c r="E43" s="2">
+        <v>1000</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>95</v>
+      </c>
+      <c r="B44" t="s">
+        <v>35</v>
+      </c>
+      <c r="C44" t="s">
+        <v>53</v>
+      </c>
+      <c r="D44" t="s">
+        <v>103</v>
+      </c>
+      <c r="E44" s="2">
+        <v>1000</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>96</v>
+      </c>
+      <c r="B45" t="s">
+        <v>36</v>
+      </c>
+      <c r="C45" t="s">
+        <v>53</v>
+      </c>
+      <c r="D45" t="s">
+        <v>103</v>
+      </c>
+      <c r="E45" s="2">
+        <v>1000</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>97</v>
+      </c>
+      <c r="B46" t="s">
+        <v>37</v>
+      </c>
+      <c r="C46" t="s">
+        <v>53</v>
+      </c>
+      <c r="D46" t="s">
+        <v>103</v>
+      </c>
+      <c r="E46" s="2">
+        <v>1000</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>98</v>
+      </c>
+      <c r="B47" t="s">
+        <v>38</v>
+      </c>
+      <c r="C47" t="s">
+        <v>53</v>
+      </c>
+      <c r="D47" t="s">
+        <v>103</v>
+      </c>
+      <c r="E47" s="2">
+        <v>1000</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>99</v>
+      </c>
+      <c r="B48" t="s">
+        <v>39</v>
+      </c>
+      <c r="C48" t="s">
+        <v>53</v>
+      </c>
+      <c r="D48" t="s">
+        <v>103</v>
+      </c>
+      <c r="E48" s="2">
+        <v>1000</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>100</v>
+      </c>
+      <c r="B49" t="s">
+        <v>40</v>
+      </c>
+      <c r="C49" t="s">
+        <v>53</v>
+      </c>
+      <c r="D49" t="s">
+        <v>103</v>
+      </c>
+      <c r="E49" s="2">
+        <v>1021</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>119</v>
+      </c>
+      <c r="B50" t="s">
+        <v>41</v>
+      </c>
+      <c r="C50" t="s">
         <v>118</v>
       </c>
-      <c r="D24" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>18</v>
-      </c>
-      <c r="B25" t="s">
-        <v>52</v>
-      </c>
-      <c r="C25" t="s">
-        <v>78</v>
-      </c>
-      <c r="D25" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>19</v>
-      </c>
-      <c r="B26" t="s">
-        <v>52</v>
-      </c>
-      <c r="C26" t="s">
-        <v>79</v>
-      </c>
-      <c r="D26" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>20</v>
-      </c>
-      <c r="B27" t="s">
-        <v>52</v>
-      </c>
-      <c r="C27" t="s">
-        <v>80</v>
-      </c>
-      <c r="D27" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>21</v>
-      </c>
-      <c r="B28" t="s">
-        <v>52</v>
-      </c>
-      <c r="C28" t="s">
-        <v>81</v>
-      </c>
-      <c r="D28" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>22</v>
-      </c>
-      <c r="B29" t="s">
-        <v>52</v>
-      </c>
-      <c r="C29" t="s">
-        <v>82</v>
-      </c>
-      <c r="D29" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>23</v>
-      </c>
-      <c r="B30" t="s">
-        <v>52</v>
-      </c>
-      <c r="C30" t="s">
-        <v>83</v>
-      </c>
-      <c r="D30" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>24</v>
-      </c>
-      <c r="B31" t="s">
-        <v>52</v>
-      </c>
-      <c r="C31" t="s">
-        <v>84</v>
-      </c>
-      <c r="D31" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>25</v>
-      </c>
-      <c r="B32" t="s">
-        <v>52</v>
-      </c>
-      <c r="C32" t="s">
-        <v>85</v>
-      </c>
-      <c r="D32" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>26</v>
-      </c>
-      <c r="B33" t="s">
-        <v>53</v>
-      </c>
-      <c r="C33" t="s">
-        <v>86</v>
-      </c>
-      <c r="D33" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>27</v>
-      </c>
-      <c r="B34" t="s">
-        <v>53</v>
-      </c>
-      <c r="C34" t="s">
-        <v>87</v>
-      </c>
-      <c r="D34" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>28</v>
-      </c>
-      <c r="B35" t="s">
-        <v>53</v>
-      </c>
-      <c r="C35" t="s">
-        <v>88</v>
-      </c>
-      <c r="D35" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>29</v>
-      </c>
-      <c r="B36" t="s">
-        <v>53</v>
-      </c>
-      <c r="C36" t="s">
-        <v>89</v>
-      </c>
-      <c r="D36" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>30</v>
-      </c>
-      <c r="B37" t="s">
-        <v>53</v>
-      </c>
-      <c r="C37" t="s">
-        <v>90</v>
-      </c>
-      <c r="D37" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>31</v>
-      </c>
-      <c r="B38" t="s">
-        <v>53</v>
-      </c>
-      <c r="C38" t="s">
-        <v>91</v>
-      </c>
-      <c r="D38" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>32</v>
-      </c>
-      <c r="B39" t="s">
-        <v>54</v>
-      </c>
-      <c r="C39" t="s">
-        <v>92</v>
-      </c>
-      <c r="D39" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>33</v>
-      </c>
-      <c r="B40" t="s">
-        <v>54</v>
-      </c>
-      <c r="C40" t="s">
-        <v>93</v>
-      </c>
-      <c r="D40" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>34</v>
-      </c>
-      <c r="B41" t="s">
-        <v>55</v>
-      </c>
-      <c r="C41" t="s">
-        <v>94</v>
-      </c>
-      <c r="D41" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>35</v>
-      </c>
-      <c r="B42" t="s">
-        <v>55</v>
-      </c>
-      <c r="C42" t="s">
-        <v>95</v>
-      </c>
-      <c r="D42" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>36</v>
-      </c>
-      <c r="B43" t="s">
-        <v>55</v>
-      </c>
-      <c r="C43" t="s">
-        <v>96</v>
-      </c>
-      <c r="D43" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>37</v>
-      </c>
-      <c r="B44" t="s">
-        <v>55</v>
-      </c>
-      <c r="C44" t="s">
-        <v>97</v>
-      </c>
-      <c r="D44" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>38</v>
-      </c>
-      <c r="B45" t="s">
-        <v>55</v>
-      </c>
-      <c r="C45" t="s">
-        <v>98</v>
-      </c>
-      <c r="D45" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>39</v>
-      </c>
-      <c r="B46" t="s">
-        <v>55</v>
-      </c>
-      <c r="C46" t="s">
-        <v>99</v>
-      </c>
-      <c r="D46" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>40</v>
-      </c>
-      <c r="B47" t="s">
-        <v>55</v>
-      </c>
-      <c r="C47" t="s">
-        <v>100</v>
-      </c>
-      <c r="D47" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
-        <v>41</v>
-      </c>
-      <c r="B48" t="s">
-        <v>55</v>
-      </c>
-      <c r="C48" t="s">
-        <v>101</v>
-      </c>
-      <c r="D48" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
+      <c r="D50" t="s">
+        <v>112</v>
+      </c>
+      <c r="E50" s="2">
+        <v>1021</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>120</v>
+      </c>
+      <c r="B51" t="s">
         <v>42</v>
       </c>
-      <c r="B49" t="s">
-        <v>55</v>
-      </c>
-      <c r="C49" t="s">
-        <v>102</v>
-      </c>
-      <c r="D49" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
+      <c r="C51" t="s">
+        <v>118</v>
+      </c>
+      <c r="D51" t="s">
+        <v>112</v>
+      </c>
+      <c r="E51" s="2">
+        <v>1021</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>121</v>
+      </c>
+      <c r="B52" t="s">
         <v>43</v>
       </c>
-      <c r="B50" t="s">
-        <v>120</v>
-      </c>
-      <c r="C50" t="s">
-        <v>121</v>
-      </c>
-      <c r="D50" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
+      <c r="C52" t="s">
+        <v>118</v>
+      </c>
+      <c r="D52" t="s">
+        <v>112</v>
+      </c>
+      <c r="E52" s="2">
+        <v>1021</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>122</v>
+      </c>
+      <c r="B53" t="s">
         <v>44</v>
       </c>
-      <c r="B51" t="s">
-        <v>120</v>
-      </c>
-      <c r="C51" t="s">
-        <v>122</v>
-      </c>
-      <c r="D51" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
+      <c r="C53" t="s">
+        <v>118</v>
+      </c>
+      <c r="D53" t="s">
+        <v>112</v>
+      </c>
+      <c r="E53" s="2">
+        <v>1021</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>123</v>
+      </c>
+      <c r="B54" t="s">
         <v>45</v>
       </c>
-      <c r="B52" t="s">
-        <v>120</v>
-      </c>
-      <c r="C52" t="s">
-        <v>123</v>
-      </c>
-      <c r="D52" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
-        <v>46</v>
-      </c>
-      <c r="B53" t="s">
-        <v>120</v>
-      </c>
-      <c r="C53" t="s">
-        <v>124</v>
-      </c>
-      <c r="D53" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
-        <v>47</v>
-      </c>
-      <c r="B54" t="s">
-        <v>120</v>
-      </c>
       <c r="C54" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="D54" t="s">
-        <v>114</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="E54" s="2">
+        <v>1021</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{3F5D65B2-ACC5-43C2-B882-3BAABAC9F7EA}">
+          <x14:formula1>
+            <xm:f>Vendor!$B$3:$B$88</xm:f>
+          </x14:formula1>
+          <xm:sqref>F40 F2:F38 F49:F54</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{5E23BA79-3716-4F83-8B78-C6AF977E5E64}">
+          <x14:formula1>
+            <xm:f>Vendor!$B$2:$B$88</xm:f>
+          </x14:formula1>
+          <xm:sqref>F41:F48 F39</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D67091F2-3670-4876-8405-3D4E218677E4}">
+  <dimension ref="A1:G40"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.33203125" customWidth="1"/>
+    <col min="2" max="2" width="25" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
+        <v>490</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>528</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>529</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="5">
+        <v>1001</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="G2" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
+        <v>1002</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="G3" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
+        <v>1003</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>532</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
+        <v>1004</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>492</v>
+      </c>
+      <c r="C5" s="3"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
+        <v>1005</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
+        <v>1006</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>494</v>
+      </c>
+      <c r="C7" s="3"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
+        <v>1007</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="C8" s="3"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
+        <v>1008</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>496</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
+        <v>1009</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>497</v>
+      </c>
+      <c r="C10" s="3"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
+        <v>1010</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>498</v>
+      </c>
+      <c r="C11" s="3"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="5">
+        <v>1011</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>499</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="5">
+        <v>1012</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>500</v>
+      </c>
+      <c r="C13" s="3"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="5">
+        <v>1013</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>501</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="5">
+        <v>1014</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>502</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="5">
+        <v>1015</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>503</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="5">
+        <v>1016</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>504</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="5">
+        <v>1017</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>505</v>
+      </c>
+      <c r="C18" s="3"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="5">
+        <v>1018</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>506</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="5">
+        <v>1019</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>507</v>
+      </c>
+      <c r="C20" s="3"/>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="5">
+        <v>1020</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>508</v>
+      </c>
+      <c r="C21" s="3"/>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="5">
+        <v>1021</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>509</v>
+      </c>
+      <c r="C22" s="3"/>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="5">
+        <v>1022</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>510</v>
+      </c>
+      <c r="C23" s="3"/>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="5">
+        <v>1023</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="C24" s="3"/>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="5">
+        <v>1024</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>512</v>
+      </c>
+      <c r="C25" s="3"/>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="5">
+        <v>1025</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>513</v>
+      </c>
+      <c r="C26" s="3"/>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="5">
+        <v>1026</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>514</v>
+      </c>
+      <c r="C27" s="3"/>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="5">
+        <v>1027</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>515</v>
+      </c>
+      <c r="C28" s="3"/>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="5">
+        <v>1028</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>516</v>
+      </c>
+      <c r="C29" s="3"/>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="5">
+        <v>1029</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>517</v>
+      </c>
+      <c r="C30" s="3"/>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="5">
+        <v>1030</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>518</v>
+      </c>
+      <c r="C31" s="3"/>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" s="5">
+        <v>1031</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>519</v>
+      </c>
+      <c r="C32" s="3"/>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="5">
+        <v>1032</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>520</v>
+      </c>
+      <c r="C33" s="3"/>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" s="5">
+        <v>1033</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C34" s="3"/>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" s="5">
+        <v>1034</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>522</v>
+      </c>
+      <c r="C35" s="3"/>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" s="5">
+        <v>1035</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>523</v>
+      </c>
+      <c r="C36" s="3"/>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" s="5">
+        <v>1036</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>524</v>
+      </c>
+      <c r="C37" s="3"/>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" s="5">
+        <v>1037</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>525</v>
+      </c>
+      <c r="C38" s="3"/>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" s="5">
+        <v>1038</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" s="5">
+        <v>1038</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>527</v>
+      </c>
+      <c r="C40" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94AAE35D-4D08-4C5E-B754-20039410A3D2}">
-  <dimension ref="A1:L33"/>
+  <dimension ref="A1:L35"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.44140625" bestFit="1" customWidth="1"/>
@@ -2690,944 +3655,999 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="K1" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1001</v>
-      </c>
-      <c r="B2" t="s">
-        <v>138</v>
-      </c>
-      <c r="C2" t="s">
-        <v>139</v>
-      </c>
-      <c r="E2" t="s">
-        <v>140</v>
-      </c>
-      <c r="F2" t="s">
-        <v>141</v>
-      </c>
-      <c r="G2" t="s">
-        <v>142</v>
-      </c>
-      <c r="H2" t="s">
-        <v>143</v>
-      </c>
-      <c r="I2">
-        <v>8453586446</v>
-      </c>
-      <c r="J2" t="s">
-        <v>144</v>
-      </c>
-      <c r="K2" t="s">
-        <v>145</v>
-      </c>
+    </row>
+    <row r="2" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="8">
+        <v>1000</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>545</v>
+      </c>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B3" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="C3" t="s">
-        <v>147</v>
-      </c>
-      <c r="D3">
-        <v>411</v>
+        <v>137</v>
       </c>
       <c r="E3" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="F3" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="G3" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="H3" t="s">
+        <v>141</v>
+      </c>
+      <c r="I3">
+        <v>8453586446</v>
+      </c>
+      <c r="J3" t="s">
+        <v>142</v>
+      </c>
+      <c r="K3" t="s">
         <v>143</v>
-      </c>
-      <c r="I3">
-        <v>9148049101</v>
-      </c>
-      <c r="J3" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B4" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="C4" t="s">
-        <v>153</v>
+        <v>145</v>
+      </c>
+      <c r="D4">
+        <v>411</v>
       </c>
       <c r="E4" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="F4" t="s">
+        <v>147</v>
+      </c>
+      <c r="G4" t="s">
+        <v>148</v>
+      </c>
+      <c r="H4" t="s">
         <v>141</v>
       </c>
-      <c r="G4" t="s">
-        <v>155</v>
-      </c>
-      <c r="H4" t="s">
-        <v>143</v>
-      </c>
       <c r="I4">
-        <v>8453594633</v>
+        <v>9148049101</v>
       </c>
       <c r="J4" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B5" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="C5" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="E5" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="F5" t="s">
+        <v>139</v>
+      </c>
+      <c r="G5" t="s">
+        <v>153</v>
+      </c>
+      <c r="H5" t="s">
         <v>141</v>
       </c>
-      <c r="G5" t="s">
-        <v>160</v>
-      </c>
-      <c r="H5" t="s">
-        <v>143</v>
-      </c>
       <c r="I5">
-        <v>5182735800</v>
+        <v>8453594633</v>
       </c>
       <c r="J5" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B6" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="C6" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="E6" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="F6" t="s">
+        <v>139</v>
+      </c>
+      <c r="G6" t="s">
+        <v>158</v>
+      </c>
+      <c r="H6" t="s">
         <v>141</v>
       </c>
-      <c r="G6" t="s">
-        <v>165</v>
-      </c>
-      <c r="H6" t="s">
-        <v>143</v>
-      </c>
       <c r="I6">
-        <v>8453594633</v>
+        <v>5182735800</v>
       </c>
       <c r="J6" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B7" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="C7" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="E7" t="s">
+        <v>162</v>
+      </c>
+      <c r="F7" t="s">
+        <v>139</v>
+      </c>
+      <c r="G7" t="s">
+        <v>163</v>
+      </c>
+      <c r="H7" t="s">
+        <v>141</v>
+      </c>
+      <c r="I7">
+        <v>8453594633</v>
+      </c>
+      <c r="J7" t="s">
         <v>164</v>
-      </c>
-      <c r="F7" t="s">
-        <v>141</v>
-      </c>
-      <c r="G7" t="s">
-        <v>165</v>
-      </c>
-      <c r="H7" t="s">
-        <v>143</v>
-      </c>
-      <c r="I7">
-        <v>8452794270</v>
-      </c>
-      <c r="J7" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B8" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="C8" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="E8" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="F8" t="s">
+        <v>139</v>
+      </c>
+      <c r="G8" t="s">
+        <v>163</v>
+      </c>
+      <c r="H8" t="s">
         <v>141</v>
       </c>
-      <c r="G8" t="s">
-        <v>173</v>
-      </c>
-      <c r="H8" t="s">
-        <v>143</v>
-      </c>
       <c r="I8">
-        <v>9146824477</v>
+        <v>8452794270</v>
       </c>
       <c r="J8" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="B9" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="C9" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="E9" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="F9" t="s">
-        <v>178</v>
+        <v>139</v>
       </c>
       <c r="G9" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="H9" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="I9">
-        <v>2037918087</v>
+        <v>9146824477</v>
       </c>
       <c r="J9" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="B10" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="C10" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="E10" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="F10" t="s">
+        <v>176</v>
+      </c>
+      <c r="G10" t="s">
+        <v>177</v>
+      </c>
+      <c r="H10" t="s">
         <v>141</v>
       </c>
-      <c r="G10" t="s">
-        <v>184</v>
-      </c>
-      <c r="H10" t="s">
-        <v>143</v>
-      </c>
       <c r="I10">
-        <v>8453745966</v>
+        <v>2037918087</v>
       </c>
       <c r="J10" t="s">
-        <v>185</v>
-      </c>
-      <c r="K10" t="s">
-        <v>286</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B11" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="C11" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="E11" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="F11" t="s">
+        <v>139</v>
+      </c>
+      <c r="G11" t="s">
+        <v>182</v>
+      </c>
+      <c r="H11" t="s">
         <v>141</v>
       </c>
-      <c r="G11" t="s">
-        <v>189</v>
-      </c>
-      <c r="H11" t="s">
-        <v>143</v>
-      </c>
       <c r="I11">
-        <v>8456924486</v>
+        <v>8453745966</v>
       </c>
       <c r="J11" t="s">
-        <v>190</v>
+        <v>183</v>
+      </c>
+      <c r="K11" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B12" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="C12" t="s">
-        <v>192</v>
-      </c>
-      <c r="D12" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="E12" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="F12" t="s">
+        <v>139</v>
+      </c>
+      <c r="G12" t="s">
+        <v>187</v>
+      </c>
+      <c r="H12" t="s">
         <v>141</v>
       </c>
-      <c r="G12" t="s">
-        <v>195</v>
-      </c>
-      <c r="H12" t="s">
-        <v>143</v>
-      </c>
       <c r="I12">
-        <v>8457658997</v>
+        <v>8456924486</v>
       </c>
       <c r="J12" t="s">
-        <v>196</v>
-      </c>
-      <c r="K12" t="s">
-        <v>287</v>
+        <v>188</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="B13" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="C13" t="s">
-        <v>198</v>
+        <v>190</v>
+      </c>
+      <c r="D13" t="s">
+        <v>191</v>
       </c>
       <c r="E13" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="F13" t="s">
+        <v>139</v>
+      </c>
+      <c r="G13" t="s">
+        <v>193</v>
+      </c>
+      <c r="H13" t="s">
         <v>141</v>
       </c>
-      <c r="G13" t="s">
-        <v>200</v>
-      </c>
-      <c r="H13" t="s">
-        <v>143</v>
-      </c>
       <c r="I13">
-        <v>8457782986</v>
+        <v>8457658997</v>
       </c>
       <c r="J13" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="K13" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B14" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="C14" t="s">
-        <v>203</v>
-      </c>
-      <c r="D14" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="E14" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="F14" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="G14" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="H14" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="I14">
-        <v>9087071234</v>
+        <v>8457782986</v>
       </c>
       <c r="J14" t="s">
-        <v>207</v>
+        <v>199</v>
+      </c>
+      <c r="K14" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="B15" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="C15" t="s">
-        <v>139</v>
+        <v>201</v>
+      </c>
+      <c r="D15" t="s">
+        <v>202</v>
       </c>
       <c r="E15" t="s">
-        <v>140</v>
+        <v>203</v>
       </c>
       <c r="F15" t="s">
+        <v>147</v>
+      </c>
+      <c r="G15" t="s">
+        <v>204</v>
+      </c>
+      <c r="H15" t="s">
         <v>141</v>
       </c>
-      <c r="G15" t="s">
-        <v>142</v>
-      </c>
-      <c r="H15" t="s">
-        <v>143</v>
-      </c>
       <c r="I15">
-        <v>8453586446</v>
+        <v>9087071234</v>
       </c>
       <c r="J15" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="B16" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C16" t="s">
-        <v>211</v>
+        <v>137</v>
       </c>
       <c r="E16" t="s">
-        <v>212</v>
+        <v>138</v>
       </c>
       <c r="F16" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="G16" t="s">
-        <v>213</v>
+        <v>140</v>
       </c>
       <c r="H16" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="I16">
-        <v>9733050022</v>
+        <v>8453586446</v>
       </c>
       <c r="J16" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="B17" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="C17" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="E17" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="F17" t="s">
+        <v>147</v>
+      </c>
+      <c r="G17" t="s">
+        <v>211</v>
+      </c>
+      <c r="H17" t="s">
         <v>141</v>
       </c>
-      <c r="G17" t="s">
-        <v>200</v>
-      </c>
-      <c r="H17" t="s">
-        <v>143</v>
-      </c>
       <c r="I17">
-        <v>8457782997</v>
+        <v>9733050022</v>
       </c>
       <c r="J17" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="B18" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C18" t="s">
-        <v>217</v>
+        <v>196</v>
       </c>
       <c r="E18" t="s">
-        <v>218</v>
+        <v>197</v>
       </c>
       <c r="F18" t="s">
-        <v>219</v>
+        <v>139</v>
       </c>
       <c r="G18" t="s">
-        <v>220</v>
+        <v>198</v>
       </c>
       <c r="H18" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="I18">
-        <v>6153551028</v>
+        <v>8457782997</v>
       </c>
       <c r="J18" t="s">
-        <v>221</v>
-      </c>
-      <c r="K18" t="s">
-        <v>222</v>
+        <v>199</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="B19" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="C19" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="E19" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="F19" t="s">
+        <v>217</v>
+      </c>
+      <c r="G19" t="s">
+        <v>218</v>
+      </c>
+      <c r="H19" t="s">
         <v>141</v>
       </c>
-      <c r="G19" t="s">
-        <v>226</v>
-      </c>
-      <c r="H19" t="s">
-        <v>143</v>
-      </c>
       <c r="I19">
-        <v>6314587019</v>
+        <v>6153551028</v>
       </c>
       <c r="J19" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="K19" t="s">
-        <v>289</v>
+        <v>220</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="B20" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="C20" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="E20" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="F20" t="s">
+        <v>139</v>
+      </c>
+      <c r="G20" t="s">
+        <v>224</v>
+      </c>
+      <c r="H20" t="s">
         <v>141</v>
       </c>
-      <c r="G20" t="s">
-        <v>231</v>
-      </c>
-      <c r="H20" t="s">
-        <v>143</v>
-      </c>
       <c r="I20">
-        <v>8452504001</v>
+        <v>6314587019</v>
       </c>
       <c r="J20" t="s">
-        <v>232</v>
+        <v>225</v>
+      </c>
+      <c r="K20" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="B21" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="C21" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="E21" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="F21" t="s">
-        <v>236</v>
+        <v>139</v>
       </c>
       <c r="G21" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="H21" t="s">
-        <v>143</v>
+        <v>141</v>
+      </c>
+      <c r="I21">
+        <v>8452504001</v>
+      </c>
+      <c r="J21" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B22" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="C22" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="E22" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="F22" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="G22" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="H22" t="s">
-        <v>143</v>
-      </c>
-      <c r="I22">
-        <v>5184383976</v>
-      </c>
-      <c r="J22" t="s">
-        <v>243</v>
-      </c>
-      <c r="K22" t="s">
-        <v>244</v>
+        <v>141</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="B23" t="s">
-        <v>245</v>
+        <v>236</v>
+      </c>
+      <c r="C23" t="s">
+        <v>237</v>
+      </c>
+      <c r="E23" t="s">
+        <v>238</v>
+      </c>
+      <c r="F23" t="s">
+        <v>239</v>
+      </c>
+      <c r="G23" t="s">
+        <v>240</v>
       </c>
       <c r="H23" t="s">
-        <v>143</v>
+        <v>141</v>
+      </c>
+      <c r="I23">
+        <v>5184383976</v>
       </c>
       <c r="J23" t="s">
-        <v>246</v>
+        <v>241</v>
+      </c>
+      <c r="K23" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="B24" t="s">
-        <v>247</v>
-      </c>
-      <c r="C24" t="s">
-        <v>248</v>
-      </c>
-      <c r="E24" t="s">
-        <v>249</v>
-      </c>
-      <c r="F24" t="s">
-        <v>250</v>
-      </c>
-      <c r="G24" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="H24" t="s">
-        <v>143</v>
+        <v>141</v>
+      </c>
+      <c r="J24" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="B25" t="s">
-        <v>252</v>
+        <v>245</v>
+      </c>
+      <c r="C25" t="s">
+        <v>246</v>
+      </c>
+      <c r="E25" t="s">
+        <v>247</v>
+      </c>
+      <c r="F25" t="s">
+        <v>248</v>
+      </c>
+      <c r="G25" t="s">
+        <v>249</v>
       </c>
       <c r="H25" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="B26" t="s">
-        <v>253</v>
-      </c>
-      <c r="C26" t="s">
-        <v>254</v>
-      </c>
-      <c r="E26" t="s">
-        <v>255</v>
-      </c>
-      <c r="F26" t="s">
+        <v>250</v>
+      </c>
+      <c r="H26" t="s">
         <v>141</v>
-      </c>
-      <c r="G26" t="s">
-        <v>256</v>
-      </c>
-      <c r="H26" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B27" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="C27" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="E27" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="F27" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="G27" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="H27" t="s">
-        <v>143</v>
-      </c>
-      <c r="I27">
-        <v>8453622300</v>
-      </c>
-      <c r="J27" t="s">
-        <v>261</v>
+        <v>141</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="B28" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="C28" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="E28" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="F28" t="s">
-        <v>265</v>
+        <v>147</v>
       </c>
       <c r="G28" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="H28" t="s">
-        <v>143</v>
+        <v>141</v>
+      </c>
+      <c r="I28">
+        <v>8453622300</v>
+      </c>
+      <c r="J28" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="B29" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="C29" t="s">
-        <v>268</v>
-      </c>
-      <c r="D29" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="E29" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="F29" t="s">
-        <v>149</v>
+        <v>263</v>
       </c>
       <c r="G29" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="H29" t="s">
-        <v>143</v>
-      </c>
-      <c r="I29">
-        <v>7323831950</v>
+        <v>141</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="B30" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="C30" t="s">
-        <v>273</v>
+        <v>266</v>
+      </c>
+      <c r="D30" t="s">
+        <v>267</v>
       </c>
       <c r="E30" t="s">
-        <v>140</v>
+        <v>268</v>
       </c>
       <c r="F30" t="s">
+        <v>147</v>
+      </c>
+      <c r="G30" t="s">
+        <v>269</v>
+      </c>
+      <c r="H30" t="s">
         <v>141</v>
       </c>
-      <c r="G30" t="s">
-        <v>142</v>
-      </c>
-      <c r="H30" t="s">
-        <v>143</v>
-      </c>
       <c r="I30">
-        <v>8453532220</v>
-      </c>
-      <c r="J30" t="s">
-        <v>274</v>
+        <v>7323831950</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B31" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="C31" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="E31" t="s">
-        <v>277</v>
+        <v>138</v>
       </c>
       <c r="F31" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="G31" t="s">
-        <v>278</v>
+        <v>140</v>
       </c>
       <c r="H31" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="I31">
-        <v>2017673200</v>
+        <v>8453532220</v>
       </c>
       <c r="J31" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32">
+        <v>1030</v>
+      </c>
+      <c r="B32" t="s">
+        <v>273</v>
+      </c>
+      <c r="C32" t="s">
+        <v>274</v>
+      </c>
+      <c r="E32" t="s">
+        <v>275</v>
+      </c>
+      <c r="F32" t="s">
+        <v>147</v>
+      </c>
+      <c r="G32" t="s">
+        <v>276</v>
+      </c>
+      <c r="H32" t="s">
+        <v>141</v>
+      </c>
+      <c r="I32">
+        <v>2017673200</v>
+      </c>
+      <c r="J32" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A33">
         <v>1031</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B33" t="s">
+        <v>278</v>
+      </c>
+      <c r="C33" t="s">
+        <v>279</v>
+      </c>
+      <c r="E33" t="s">
         <v>280</v>
       </c>
-      <c r="C32" t="s">
+      <c r="F33" t="s">
+        <v>147</v>
+      </c>
+      <c r="G33" t="s">
         <v>281</v>
       </c>
-      <c r="E32" t="s">
+      <c r="H33" t="s">
+        <v>141</v>
+      </c>
+      <c r="I33">
+        <v>8456236423</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <v>1032</v>
+      </c>
+      <c r="B34" t="s">
         <v>282</v>
       </c>
-      <c r="F32" t="s">
-        <v>149</v>
-      </c>
-      <c r="G32" t="s">
+      <c r="C34" t="s">
         <v>283</v>
       </c>
-      <c r="H32" t="s">
-        <v>143</v>
-      </c>
-      <c r="I32">
-        <v>8456236423</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A33">
-        <v>1032</v>
-      </c>
-      <c r="B33" t="s">
-        <v>284</v>
-      </c>
-      <c r="C33" t="s">
-        <v>285</v>
-      </c>
-      <c r="E33" t="s">
-        <v>154</v>
-      </c>
-      <c r="F33" t="s">
+      <c r="E34" t="s">
+        <v>152</v>
+      </c>
+      <c r="F34" t="s">
+        <v>139</v>
+      </c>
+      <c r="G34" t="s">
+        <v>153</v>
+      </c>
+      <c r="H34" t="s">
         <v>141</v>
       </c>
-      <c r="G33" t="s">
-        <v>155</v>
-      </c>
-      <c r="H33" t="s">
-        <v>143</v>
-      </c>
-      <c r="I33">
+      <c r="I34">
         <v>8453561700</v>
       </c>
     </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <v>1033</v>
+      </c>
+      <c r="B35" t="s">
+        <v>538</v>
+      </c>
+      <c r="C35" t="s">
+        <v>539</v>
+      </c>
+      <c r="E35" t="s">
+        <v>540</v>
+      </c>
+      <c r="F35" t="s">
+        <v>139</v>
+      </c>
+      <c r="G35">
+        <v>10960</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="I35">
+        <v>8453589763</v>
+      </c>
+      <c r="J35" t="s">
+        <v>541</v>
+      </c>
+      <c r="K35" t="s">
+        <v>542</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="J2" r:id="rId1" xr:uid="{6DDE6C53-807A-4DDA-80CB-3E2DF3C97F69}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4820533E-391C-4DD0-BE90-F683AEF9F4DB}">
   <dimension ref="A1:L30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3647,41 +4667,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="G1" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>295</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
@@ -3689,7 +4709,7 @@
         <v>21108</v>
       </c>
       <c r="B2" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C2">
         <v>954500</v>
@@ -3701,13 +4721,13 @@
         <v>5</v>
       </c>
       <c r="G2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="H2" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="I2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J2">
         <v>10507</v>
@@ -3721,7 +4741,7 @@
         <v>23072</v>
       </c>
       <c r="B3" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C3">
         <v>173000</v>
@@ -3733,13 +4753,13 @@
         <v>5</v>
       </c>
       <c r="G3" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="H3" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="I3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J3">
         <v>10921</v>
@@ -3753,7 +4773,7 @@
         <v>23099</v>
       </c>
       <c r="B4" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C4">
         <v>315000</v>
@@ -3765,13 +4785,13 @@
         <v>5</v>
       </c>
       <c r="G4" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="H4" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="I4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J4">
         <v>12550</v>
@@ -3785,7 +4805,7 @@
         <v>23108</v>
       </c>
       <c r="B5" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C5">
         <v>299500</v>
@@ -3797,13 +4817,13 @@
         <v>5</v>
       </c>
       <c r="G5" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="H5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="I5" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J5">
         <v>10590</v>
@@ -3817,7 +4837,7 @@
         <v>24021</v>
       </c>
       <c r="B6" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C6">
         <v>2700000</v>
@@ -3829,16 +4849,16 @@
         <v>5</v>
       </c>
       <c r="G6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H6" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="I6" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J6" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="L6">
         <v>1002</v>
@@ -3849,7 +4869,7 @@
         <v>24027</v>
       </c>
       <c r="B7" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C7">
         <v>108000</v>
@@ -3861,16 +4881,16 @@
         <v>5</v>
       </c>
       <c r="G7" t="s">
+        <v>312</v>
+      </c>
+      <c r="H7" t="s">
+        <v>313</v>
+      </c>
+      <c r="I7" t="s">
+        <v>139</v>
+      </c>
+      <c r="J7" t="s">
         <v>314</v>
-      </c>
-      <c r="H7" t="s">
-        <v>315</v>
-      </c>
-      <c r="I7" t="s">
-        <v>141</v>
-      </c>
-      <c r="J7" t="s">
-        <v>316</v>
       </c>
       <c r="L7">
         <v>1009</v>
@@ -3881,7 +4901,7 @@
         <v>24030</v>
       </c>
       <c r="B8" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C8">
         <v>25600</v>
@@ -3893,16 +4913,16 @@
         <v>5</v>
       </c>
       <c r="G8" t="s">
+        <v>316</v>
+      </c>
+      <c r="H8" t="s">
+        <v>317</v>
+      </c>
+      <c r="I8" t="s">
+        <v>139</v>
+      </c>
+      <c r="J8" t="s">
         <v>318</v>
-      </c>
-      <c r="H8" t="s">
-        <v>319</v>
-      </c>
-      <c r="I8" t="s">
-        <v>141</v>
-      </c>
-      <c r="J8" t="s">
-        <v>320</v>
       </c>
       <c r="L8">
         <v>1001</v>
@@ -3913,7 +4933,7 @@
         <v>24047</v>
       </c>
       <c r="B9" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C9">
         <v>65785</v>
@@ -3925,16 +4945,16 @@
         <v>5</v>
       </c>
       <c r="G9" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="H9" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="I9" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J9" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="L9">
         <v>1009</v>
@@ -3945,7 +4965,7 @@
         <v>24053</v>
       </c>
       <c r="B10" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C10">
         <v>269000</v>
@@ -3957,16 +4977,16 @@
         <v>5</v>
       </c>
       <c r="G10" t="s">
+        <v>322</v>
+      </c>
+      <c r="H10" t="s">
+        <v>323</v>
+      </c>
+      <c r="I10" t="s">
+        <v>139</v>
+      </c>
+      <c r="J10" t="s">
         <v>324</v>
-      </c>
-      <c r="H10" t="s">
-        <v>325</v>
-      </c>
-      <c r="I10" t="s">
-        <v>141</v>
-      </c>
-      <c r="J10" t="s">
-        <v>326</v>
       </c>
       <c r="L10">
         <v>1004</v>
@@ -3977,7 +4997,7 @@
         <v>24059</v>
       </c>
       <c r="B11" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C11">
         <v>148000</v>
@@ -3989,16 +5009,16 @@
         <v>5</v>
       </c>
       <c r="G11" t="s">
+        <v>326</v>
+      </c>
+      <c r="H11" t="s">
+        <v>327</v>
+      </c>
+      <c r="I11" t="s">
+        <v>139</v>
+      </c>
+      <c r="J11" t="s">
         <v>328</v>
-      </c>
-      <c r="H11" t="s">
-        <v>329</v>
-      </c>
-      <c r="I11" t="s">
-        <v>141</v>
-      </c>
-      <c r="J11" t="s">
-        <v>330</v>
       </c>
       <c r="L11">
         <v>1006</v>
@@ -4009,7 +5029,7 @@
         <v>24062</v>
       </c>
       <c r="B12" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C12">
         <v>84320</v>
@@ -4021,16 +5041,16 @@
         <v>5</v>
       </c>
       <c r="G12" t="s">
+        <v>330</v>
+      </c>
+      <c r="H12" t="s">
+        <v>331</v>
+      </c>
+      <c r="I12" t="s">
+        <v>139</v>
+      </c>
+      <c r="J12" t="s">
         <v>332</v>
-      </c>
-      <c r="H12" t="s">
-        <v>333</v>
-      </c>
-      <c r="I12" t="s">
-        <v>141</v>
-      </c>
-      <c r="J12" t="s">
-        <v>334</v>
       </c>
       <c r="L12">
         <v>1007</v>
@@ -4041,7 +5061,7 @@
         <v>24073</v>
       </c>
       <c r="B13" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C13">
         <v>68100</v>
@@ -4053,16 +5073,16 @@
         <v>5</v>
       </c>
       <c r="G13" t="s">
+        <v>334</v>
+      </c>
+      <c r="H13" t="s">
+        <v>335</v>
+      </c>
+      <c r="I13" t="s">
+        <v>139</v>
+      </c>
+      <c r="J13" t="s">
         <v>336</v>
-      </c>
-      <c r="H13" t="s">
-        <v>337</v>
-      </c>
-      <c r="I13" t="s">
-        <v>141</v>
-      </c>
-      <c r="J13" t="s">
-        <v>338</v>
       </c>
       <c r="L13">
         <v>1006</v>
@@ -4073,7 +5093,7 @@
         <v>24130</v>
       </c>
       <c r="B14" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C14">
         <v>152000</v>
@@ -4085,16 +5105,16 @@
         <v>5</v>
       </c>
       <c r="G14" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="H14" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="I14" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J14" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="L14">
         <v>1003</v>
@@ -4105,7 +5125,7 @@
         <v>24120</v>
       </c>
       <c r="B15" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C15">
         <v>68500</v>
@@ -4117,16 +5137,16 @@
         <v>5</v>
       </c>
       <c r="G15" t="s">
+        <v>341</v>
+      </c>
+      <c r="H15" t="s">
+        <v>342</v>
+      </c>
+      <c r="I15" t="s">
+        <v>139</v>
+      </c>
+      <c r="J15" t="s">
         <v>343</v>
-      </c>
-      <c r="H15" t="s">
-        <v>344</v>
-      </c>
-      <c r="I15" t="s">
-        <v>141</v>
-      </c>
-      <c r="J15" t="s">
-        <v>345</v>
       </c>
       <c r="L15">
         <v>1009</v>
@@ -4137,7 +5157,7 @@
         <v>24058</v>
       </c>
       <c r="B16" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C16">
         <v>418000</v>
@@ -4149,16 +5169,16 @@
         <v>5</v>
       </c>
       <c r="G16" t="s">
+        <v>345</v>
+      </c>
+      <c r="H16" t="s">
+        <v>346</v>
+      </c>
+      <c r="I16" t="s">
+        <v>139</v>
+      </c>
+      <c r="J16" t="s">
         <v>347</v>
-      </c>
-      <c r="H16" t="s">
-        <v>348</v>
-      </c>
-      <c r="I16" t="s">
-        <v>141</v>
-      </c>
-      <c r="J16" t="s">
-        <v>349</v>
       </c>
       <c r="L16">
         <v>1010</v>
@@ -4169,7 +5189,7 @@
         <v>24119</v>
       </c>
       <c r="B17" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C17">
         <v>15500</v>
@@ -4181,16 +5201,16 @@
         <v>5</v>
       </c>
       <c r="G17" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="H17" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="I17" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J17" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="L17">
         <v>1009</v>
@@ -4201,7 +5221,7 @@
         <v>24127</v>
       </c>
       <c r="B18" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C18">
         <v>557500</v>
@@ -4213,16 +5233,16 @@
         <v>5</v>
       </c>
       <c r="G18" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="H18" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="I18" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J18" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="L18">
         <v>1004</v>
@@ -4233,7 +5253,7 @@
         <v>24126</v>
       </c>
       <c r="B19" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C19">
         <v>1065000</v>
@@ -4245,16 +5265,16 @@
         <v>5</v>
       </c>
       <c r="G19" t="s">
+        <v>354</v>
+      </c>
+      <c r="H19" t="s">
+        <v>355</v>
+      </c>
+      <c r="I19" t="s">
+        <v>139</v>
+      </c>
+      <c r="J19" t="s">
         <v>356</v>
-      </c>
-      <c r="H19" t="s">
-        <v>357</v>
-      </c>
-      <c r="I19" t="s">
-        <v>141</v>
-      </c>
-      <c r="J19" t="s">
-        <v>358</v>
       </c>
       <c r="L19">
         <v>1008</v>
@@ -4265,7 +5285,7 @@
         <v>24124</v>
       </c>
       <c r="B20" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C20">
         <v>43000</v>
@@ -4277,16 +5297,16 @@
         <v>10</v>
       </c>
       <c r="G20" t="s">
+        <v>358</v>
+      </c>
+      <c r="H20" t="s">
+        <v>359</v>
+      </c>
+      <c r="I20" t="s">
+        <v>139</v>
+      </c>
+      <c r="J20" t="s">
         <v>360</v>
-      </c>
-      <c r="H20" t="s">
-        <v>361</v>
-      </c>
-      <c r="I20" t="s">
-        <v>141</v>
-      </c>
-      <c r="J20" t="s">
-        <v>362</v>
       </c>
       <c r="L20">
         <v>1005</v>
@@ -4297,7 +5317,7 @@
         <v>24125</v>
       </c>
       <c r="B21" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C21">
         <v>55000</v>
@@ -4309,16 +5329,16 @@
         <v>10</v>
       </c>
       <c r="G21" t="s">
+        <v>362</v>
+      </c>
+      <c r="H21" t="s">
+        <v>363</v>
+      </c>
+      <c r="I21" t="s">
+        <v>139</v>
+      </c>
+      <c r="J21" t="s">
         <v>364</v>
-      </c>
-      <c r="H21" t="s">
-        <v>365</v>
-      </c>
-      <c r="I21" t="s">
-        <v>141</v>
-      </c>
-      <c r="J21" t="s">
-        <v>366</v>
       </c>
       <c r="L21">
         <v>1005</v>
@@ -4329,7 +5349,7 @@
         <v>25032</v>
       </c>
       <c r="B22" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C22">
         <v>168500</v>
@@ -4341,16 +5361,16 @@
         <v>5</v>
       </c>
       <c r="G22" t="s">
+        <v>366</v>
+      </c>
+      <c r="H22" t="s">
+        <v>367</v>
+      </c>
+      <c r="I22" t="s">
+        <v>176</v>
+      </c>
+      <c r="J22" t="s">
         <v>368</v>
-      </c>
-      <c r="H22" t="s">
-        <v>369</v>
-      </c>
-      <c r="I22" t="s">
-        <v>178</v>
-      </c>
-      <c r="J22" t="s">
-        <v>370</v>
       </c>
       <c r="L22">
         <v>1012</v>
@@ -4361,7 +5381,7 @@
         <v>24121</v>
       </c>
       <c r="B23" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C23">
         <v>154000</v>
@@ -4373,16 +5393,16 @@
         <v>5</v>
       </c>
       <c r="G23" t="s">
+        <v>370</v>
+      </c>
+      <c r="H23" t="s">
+        <v>371</v>
+      </c>
+      <c r="I23" t="s">
+        <v>139</v>
+      </c>
+      <c r="J23" t="s">
         <v>372</v>
-      </c>
-      <c r="H23" t="s">
-        <v>373</v>
-      </c>
-      <c r="I23" t="s">
-        <v>141</v>
-      </c>
-      <c r="J23" t="s">
-        <v>374</v>
       </c>
       <c r="L23">
         <v>1011</v>
@@ -4393,7 +5413,7 @@
         <v>25019</v>
       </c>
       <c r="B24" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C24">
         <v>122500</v>
@@ -4405,16 +5425,16 @@
         <v>5</v>
       </c>
       <c r="G24" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="H24" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="I24" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J24" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="L24">
         <v>1014</v>
@@ -4425,7 +5445,7 @@
         <v>25034</v>
       </c>
       <c r="B25" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C25">
         <v>750000</v>
@@ -4437,16 +5457,16 @@
         <v>5</v>
       </c>
       <c r="G25" t="s">
+        <v>376</v>
+      </c>
+      <c r="H25" t="s">
+        <v>377</v>
+      </c>
+      <c r="I25" t="s">
+        <v>139</v>
+      </c>
+      <c r="J25" t="s">
         <v>378</v>
-      </c>
-      <c r="H25" t="s">
-        <v>379</v>
-      </c>
-      <c r="I25" t="s">
-        <v>141</v>
-      </c>
-      <c r="J25" t="s">
-        <v>380</v>
       </c>
       <c r="L25">
         <v>1017</v>
@@ -4457,7 +5477,7 @@
         <v>25012</v>
       </c>
       <c r="B26" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C26">
         <v>1299000</v>
@@ -4469,16 +5489,16 @@
         <v>5</v>
       </c>
       <c r="G26" t="s">
+        <v>380</v>
+      </c>
+      <c r="H26" t="s">
+        <v>381</v>
+      </c>
+      <c r="I26" t="s">
+        <v>139</v>
+      </c>
+      <c r="J26" t="s">
         <v>382</v>
-      </c>
-      <c r="H26" t="s">
-        <v>383</v>
-      </c>
-      <c r="I26" t="s">
-        <v>141</v>
-      </c>
-      <c r="J26" t="s">
-        <v>384</v>
       </c>
       <c r="L26">
         <v>1018</v>
@@ -4489,7 +5509,7 @@
         <v>25005</v>
       </c>
       <c r="B27" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C27">
         <v>86000</v>
@@ -4501,16 +5521,16 @@
         <v>5</v>
       </c>
       <c r="G27" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H27" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="I27" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J27" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="L27">
         <v>1013</v>
@@ -4521,7 +5541,7 @@
         <v>24084</v>
       </c>
       <c r="B28" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C28">
         <v>260000</v>
@@ -4533,16 +5553,16 @@
         <v>5</v>
       </c>
       <c r="G28" t="s">
+        <v>386</v>
+      </c>
+      <c r="H28" t="s">
+        <v>387</v>
+      </c>
+      <c r="I28" t="s">
+        <v>139</v>
+      </c>
+      <c r="J28" t="s">
         <v>388</v>
-      </c>
-      <c r="H28" t="s">
-        <v>389</v>
-      </c>
-      <c r="I28" t="s">
-        <v>141</v>
-      </c>
-      <c r="J28" t="s">
-        <v>390</v>
       </c>
       <c r="L28">
         <v>1001</v>
@@ -4553,7 +5573,7 @@
         <v>24079</v>
       </c>
       <c r="B29" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C29">
         <v>114500</v>
@@ -4565,16 +5585,16 @@
         <v>5</v>
       </c>
       <c r="G29" t="s">
+        <v>390</v>
+      </c>
+      <c r="H29" t="s">
+        <v>391</v>
+      </c>
+      <c r="I29" t="s">
+        <v>139</v>
+      </c>
+      <c r="J29" t="s">
         <v>392</v>
-      </c>
-      <c r="H29" t="s">
-        <v>393</v>
-      </c>
-      <c r="I29" t="s">
-        <v>141</v>
-      </c>
-      <c r="J29" t="s">
-        <v>394</v>
       </c>
       <c r="L29">
         <v>1016</v>
@@ -4585,7 +5605,7 @@
         <v>25050</v>
       </c>
       <c r="B30" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C30">
         <v>260000</v>
@@ -4597,16 +5617,16 @@
         <v>5</v>
       </c>
       <c r="G30" t="s">
+        <v>394</v>
+      </c>
+      <c r="H30" t="s">
+        <v>395</v>
+      </c>
+      <c r="I30" t="s">
+        <v>139</v>
+      </c>
+      <c r="J30" t="s">
         <v>396</v>
-      </c>
-      <c r="H30" t="s">
-        <v>397</v>
-      </c>
-      <c r="I30" t="s">
-        <v>141</v>
-      </c>
-      <c r="J30" t="s">
-        <v>398</v>
       </c>
       <c r="L30">
         <v>1015</v>
@@ -4617,7 +5637,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D81B1A8-9700-42C2-A604-5D476D4FE24E}">
   <dimension ref="A1:L19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4637,41 +5657,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="D1" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="J1" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>135</v>
+      <c r="L1" s="1" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
@@ -4679,25 +5699,25 @@
         <v>1001</v>
       </c>
       <c r="B2" t="s">
+        <v>402</v>
+      </c>
+      <c r="C2" t="s">
+        <v>402</v>
+      </c>
+      <c r="D2" t="s">
+        <v>403</v>
+      </c>
+      <c r="F2" t="s">
+        <v>323</v>
+      </c>
+      <c r="G2" t="s">
+        <v>139</v>
+      </c>
+      <c r="H2" t="s">
+        <v>324</v>
+      </c>
+      <c r="I2" t="s">
         <v>404</v>
-      </c>
-      <c r="C2" t="s">
-        <v>404</v>
-      </c>
-      <c r="D2" t="s">
-        <v>405</v>
-      </c>
-      <c r="F2" t="s">
-        <v>325</v>
-      </c>
-      <c r="G2" t="s">
-        <v>141</v>
-      </c>
-      <c r="H2" t="s">
-        <v>326</v>
-      </c>
-      <c r="I2" t="s">
-        <v>406</v>
       </c>
       <c r="J2">
         <v>8452948882</v>
@@ -4706,7 +5726,7 @@
         <v>8452948883</v>
       </c>
       <c r="L2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
@@ -4714,31 +5734,31 @@
         <v>1002</v>
       </c>
       <c r="B3" t="s">
+        <v>406</v>
+      </c>
+      <c r="C3" t="s">
+        <v>480</v>
+      </c>
+      <c r="D3" t="s">
+        <v>407</v>
+      </c>
+      <c r="F3" t="s">
         <v>408</v>
       </c>
-      <c r="C3" t="s">
-        <v>482</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="G3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H3" t="s">
         <v>409</v>
       </c>
-      <c r="F3" t="s">
+      <c r="I3" t="s">
         <v>410</v>
-      </c>
-      <c r="G3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H3" t="s">
-        <v>411</v>
-      </c>
-      <c r="I3" t="s">
-        <v>412</v>
       </c>
       <c r="J3">
         <v>2037978788</v>
       </c>
       <c r="L3" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
@@ -4746,31 +5766,31 @@
         <v>1003</v>
       </c>
       <c r="B4" t="s">
+        <v>412</v>
+      </c>
+      <c r="C4" t="s">
+        <v>481</v>
+      </c>
+      <c r="D4" t="s">
+        <v>413</v>
+      </c>
+      <c r="F4" t="s">
         <v>414</v>
       </c>
-      <c r="C4" t="s">
-        <v>483</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="G4" t="s">
+        <v>139</v>
+      </c>
+      <c r="H4" t="s">
         <v>415</v>
       </c>
-      <c r="F4" t="s">
+      <c r="I4" t="s">
         <v>416</v>
       </c>
-      <c r="G4" t="s">
-        <v>141</v>
-      </c>
-      <c r="H4" t="s">
+      <c r="J4" t="s">
         <v>417</v>
       </c>
-      <c r="I4" t="s">
+      <c r="L4" t="s">
         <v>418</v>
-      </c>
-      <c r="J4" t="s">
-        <v>419</v>
-      </c>
-      <c r="L4" t="s">
-        <v>420</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
@@ -4778,37 +5798,37 @@
         <v>1004</v>
       </c>
       <c r="B5" t="s">
+        <v>419</v>
+      </c>
+      <c r="C5" t="s">
+        <v>482</v>
+      </c>
+      <c r="D5" t="s">
+        <v>420</v>
+      </c>
+      <c r="E5" t="s">
         <v>421</v>
       </c>
-      <c r="C5" t="s">
-        <v>484</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="F5" t="s">
+        <v>414</v>
+      </c>
+      <c r="G5" t="s">
+        <v>139</v>
+      </c>
+      <c r="H5" t="s">
         <v>422</v>
       </c>
-      <c r="E5" t="s">
+      <c r="I5" t="s">
         <v>423</v>
       </c>
-      <c r="F5" t="s">
-        <v>416</v>
-      </c>
-      <c r="G5" t="s">
-        <v>141</v>
-      </c>
-      <c r="H5" t="s">
+      <c r="J5" t="s">
         <v>424</v>
       </c>
-      <c r="I5" t="s">
+      <c r="K5" t="s">
         <v>425</v>
       </c>
-      <c r="J5" t="s">
+      <c r="L5" t="s">
         <v>426</v>
-      </c>
-      <c r="K5" t="s">
-        <v>427</v>
-      </c>
-      <c r="L5" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
@@ -4816,31 +5836,31 @@
         <v>1005</v>
       </c>
       <c r="B6" t="s">
+        <v>427</v>
+      </c>
+      <c r="C6" t="s">
+        <v>427</v>
+      </c>
+      <c r="D6" t="s">
+        <v>428</v>
+      </c>
+      <c r="F6" t="s">
+        <v>359</v>
+      </c>
+      <c r="G6" t="s">
+        <v>139</v>
+      </c>
+      <c r="H6" t="s">
+        <v>360</v>
+      </c>
+      <c r="I6" t="s">
         <v>429</v>
       </c>
-      <c r="C6" t="s">
-        <v>429</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="J6" t="s">
         <v>430</v>
       </c>
-      <c r="F6" t="s">
-        <v>361</v>
-      </c>
-      <c r="G6" t="s">
-        <v>141</v>
-      </c>
-      <c r="H6" t="s">
-        <v>362</v>
-      </c>
-      <c r="I6" t="s">
+      <c r="L6" t="s">
         <v>431</v>
-      </c>
-      <c r="J6" t="s">
-        <v>432</v>
-      </c>
-      <c r="L6" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
@@ -4848,25 +5868,25 @@
         <v>1006</v>
       </c>
       <c r="B7" t="s">
+        <v>432</v>
+      </c>
+      <c r="C7" t="s">
+        <v>432</v>
+      </c>
+      <c r="D7" t="s">
+        <v>433</v>
+      </c>
+      <c r="F7" t="s">
         <v>434</v>
       </c>
-      <c r="C7" t="s">
-        <v>434</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="G7" t="s">
+        <v>147</v>
+      </c>
+      <c r="H7" t="s">
         <v>435</v>
       </c>
-      <c r="F7" t="s">
+      <c r="I7" t="s">
         <v>436</v>
-      </c>
-      <c r="G7" t="s">
-        <v>149</v>
-      </c>
-      <c r="H7" t="s">
-        <v>437</v>
-      </c>
-      <c r="I7" t="s">
-        <v>438</v>
       </c>
       <c r="J7">
         <v>9736890449</v>
@@ -4875,7 +5895,7 @@
         <v>9736890466</v>
       </c>
       <c r="L7" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
@@ -4883,34 +5903,34 @@
         <v>1007</v>
       </c>
       <c r="B8" t="s">
+        <v>438</v>
+      </c>
+      <c r="C8" t="s">
+        <v>483</v>
+      </c>
+      <c r="D8" t="s">
+        <v>439</v>
+      </c>
+      <c r="E8" t="s">
         <v>440</v>
       </c>
-      <c r="C8" t="s">
-        <v>485</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="F8" t="s">
         <v>441</v>
       </c>
-      <c r="E8" t="s">
+      <c r="G8" t="s">
+        <v>139</v>
+      </c>
+      <c r="H8" t="s">
         <v>442</v>
       </c>
-      <c r="F8" t="s">
+      <c r="I8" t="s">
         <v>443</v>
-      </c>
-      <c r="G8" t="s">
-        <v>141</v>
-      </c>
-      <c r="H8" t="s">
-        <v>444</v>
-      </c>
-      <c r="I8" t="s">
-        <v>445</v>
       </c>
       <c r="J8">
         <v>8442925629</v>
       </c>
       <c r="L8" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
@@ -4918,25 +5938,25 @@
         <v>1008</v>
       </c>
       <c r="B9" t="s">
+        <v>445</v>
+      </c>
+      <c r="C9" t="s">
+        <v>484</v>
+      </c>
+      <c r="D9" t="s">
+        <v>446</v>
+      </c>
+      <c r="F9" t="s">
+        <v>157</v>
+      </c>
+      <c r="G9" t="s">
+        <v>139</v>
+      </c>
+      <c r="H9" t="s">
+        <v>158</v>
+      </c>
+      <c r="I9" t="s">
         <v>447</v>
-      </c>
-      <c r="C9" t="s">
-        <v>486</v>
-      </c>
-      <c r="D9" t="s">
-        <v>448</v>
-      </c>
-      <c r="F9" t="s">
-        <v>159</v>
-      </c>
-      <c r="G9" t="s">
-        <v>141</v>
-      </c>
-      <c r="H9" t="s">
-        <v>160</v>
-      </c>
-      <c r="I9" t="s">
-        <v>449</v>
       </c>
       <c r="J9">
         <v>5182730234</v>
@@ -4945,7 +5965,7 @@
         <v>5182730245</v>
       </c>
       <c r="L9" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
@@ -4953,16 +5973,16 @@
         <v>1009</v>
       </c>
       <c r="B10" t="s">
+        <v>449</v>
+      </c>
+      <c r="C10" t="s">
+        <v>449</v>
+      </c>
+      <c r="I10" t="s">
+        <v>450</v>
+      </c>
+      <c r="L10" t="s">
         <v>451</v>
-      </c>
-      <c r="C10" t="s">
-        <v>451</v>
-      </c>
-      <c r="I10" t="s">
-        <v>452</v>
-      </c>
-      <c r="L10" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
@@ -4970,16 +5990,16 @@
         <v>1010</v>
       </c>
       <c r="B11" t="s">
+        <v>452</v>
+      </c>
+      <c r="C11" t="s">
+        <v>485</v>
+      </c>
+      <c r="I11" t="s">
+        <v>453</v>
+      </c>
+      <c r="L11" t="s">
         <v>454</v>
-      </c>
-      <c r="C11" t="s">
-        <v>487</v>
-      </c>
-      <c r="I11" t="s">
-        <v>455</v>
-      </c>
-      <c r="L11" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
@@ -4987,16 +6007,16 @@
         <v>1011</v>
       </c>
       <c r="B12" t="s">
+        <v>455</v>
+      </c>
+      <c r="C12" t="s">
+        <v>455</v>
+      </c>
+      <c r="I12" t="s">
+        <v>456</v>
+      </c>
+      <c r="L12" t="s">
         <v>457</v>
-      </c>
-      <c r="C12" t="s">
-        <v>457</v>
-      </c>
-      <c r="I12" t="s">
-        <v>458</v>
-      </c>
-      <c r="L12" t="s">
-        <v>459</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -5004,28 +6024,28 @@
         <v>1012</v>
       </c>
       <c r="B13" t="s">
+        <v>458</v>
+      </c>
+      <c r="C13" t="s">
+        <v>486</v>
+      </c>
+      <c r="D13" t="s">
+        <v>459</v>
+      </c>
+      <c r="F13" t="s">
         <v>460</v>
       </c>
-      <c r="C13" t="s">
-        <v>488</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="G13" t="s">
+        <v>139</v>
+      </c>
+      <c r="H13" t="s">
         <v>461</v>
       </c>
-      <c r="F13" t="s">
+      <c r="I13" t="s">
         <v>462</v>
       </c>
-      <c r="G13" t="s">
-        <v>141</v>
-      </c>
-      <c r="H13" t="s">
+      <c r="L13" t="s">
         <v>463</v>
-      </c>
-      <c r="I13" t="s">
-        <v>464</v>
-      </c>
-      <c r="L13" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -5033,16 +6053,16 @@
         <v>1013</v>
       </c>
       <c r="B14" t="s">
+        <v>464</v>
+      </c>
+      <c r="C14" t="s">
+        <v>464</v>
+      </c>
+      <c r="I14" t="s">
+        <v>465</v>
+      </c>
+      <c r="L14" t="s">
         <v>466</v>
-      </c>
-      <c r="C14" t="s">
-        <v>466</v>
-      </c>
-      <c r="I14" t="s">
-        <v>467</v>
-      </c>
-      <c r="L14" t="s">
-        <v>468</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
@@ -5050,16 +6070,16 @@
         <v>1014</v>
       </c>
       <c r="B15" t="s">
+        <v>467</v>
+      </c>
+      <c r="C15" t="s">
+        <v>467</v>
+      </c>
+      <c r="I15" t="s">
+        <v>468</v>
+      </c>
+      <c r="L15" t="s">
         <v>469</v>
-      </c>
-      <c r="C15" t="s">
-        <v>469</v>
-      </c>
-      <c r="I15" t="s">
-        <v>470</v>
-      </c>
-      <c r="L15" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
@@ -5067,16 +6087,16 @@
         <v>1015</v>
       </c>
       <c r="B16" t="s">
+        <v>470</v>
+      </c>
+      <c r="C16" t="s">
+        <v>470</v>
+      </c>
+      <c r="I16" t="s">
+        <v>471</v>
+      </c>
+      <c r="L16" t="s">
         <v>472</v>
-      </c>
-      <c r="C16" t="s">
-        <v>472</v>
-      </c>
-      <c r="I16" t="s">
-        <v>473</v>
-      </c>
-      <c r="L16" t="s">
-        <v>474</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
@@ -5084,16 +6104,16 @@
         <v>1016</v>
       </c>
       <c r="B17" t="s">
+        <v>473</v>
+      </c>
+      <c r="C17" t="s">
+        <v>487</v>
+      </c>
+      <c r="I17" t="s">
+        <v>474</v>
+      </c>
+      <c r="L17" t="s">
         <v>475</v>
-      </c>
-      <c r="C17" t="s">
-        <v>489</v>
-      </c>
-      <c r="I17" t="s">
-        <v>476</v>
-      </c>
-      <c r="L17" t="s">
-        <v>477</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
@@ -5101,19 +6121,19 @@
         <v>1017</v>
       </c>
       <c r="B18" t="s">
+        <v>476</v>
+      </c>
+      <c r="C18" t="s">
+        <v>477</v>
+      </c>
+      <c r="F18" t="s">
+        <v>434</v>
+      </c>
+      <c r="G18" t="s">
+        <v>147</v>
+      </c>
+      <c r="H18" t="s">
         <v>478</v>
-      </c>
-      <c r="C18" t="s">
-        <v>479</v>
-      </c>
-      <c r="F18" t="s">
-        <v>436</v>
-      </c>
-      <c r="G18" t="s">
-        <v>149</v>
-      </c>
-      <c r="H18" t="s">
-        <v>480</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
@@ -5121,7 +6141,7 @@
         <v>1018</v>
       </c>
       <c r="B19" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
   </sheetData>
